--- a/public/templates/examples/A-160-VulnerabilityScanningSchedule-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-160-VulnerabilityScanningSchedule-EXAMPLE-S.xlsx
@@ -3,11 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="22340" windowHeight="21660" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="22340" windowHeight="21660" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Schedule!$10:$10</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -15,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -195,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -260,6 +265,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -646,7 +658,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="9" t="n"/>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Authority</t>
@@ -762,7 +774,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Automated vulnerability scan</t>
@@ -788,18 +800,14 @@
           <t>County IT Administrator</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G11" s="21" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
+      <c r="F11" s="26">
+        <v>46203</v>
+      </c>
+      <c r="G11" s="28">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Authenticated / credentialed scan</t>
@@ -825,18 +833,14 @@
           <t>County IT Administrator</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G12" s="21" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
+      <c r="F12" s="26">
+        <v>46142</v>
+      </c>
+      <c r="G12" s="28">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Penetration test (independent assessor)</t>
@@ -862,18 +866,14 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="G13" s="21" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
+      <c r="F13" s="26">
+        <v>45945</v>
+      </c>
+      <c r="G13" s="28">
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Independent control assessment</t>
@@ -899,15 +899,11 @@
           <t>Director</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
-        <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="G14" s="21" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
+      <c r="F14" s="26">
+        <v>45945</v>
+      </c>
+      <c r="G14" s="28">
+        <v>46142</v>
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1">
@@ -968,7 +964,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Summary (as of 2026-05-01)</t>
         </is>
       </c>
     </row>
@@ -981,7 +977,6 @@
       <c r="B23" s="25" t="n"/>
       <c r="C23" s="13">
         <f>COUNTA(A11:A20)</f>
-        <v/>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
@@ -992,8 +987,7 @@
       </c>
       <c r="B24" s="25" t="n"/>
       <c r="C24" s="13">
-        <f>COUNTIF(G11:G20,"&lt;"&amp;TODAY())</f>
-        <v/>
+        <f>COUNTIF(G11:G20,"&lt;"&amp;DATE(2026,5,1))</f>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -1012,7 +1006,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="9" t="n"/>
     </row>
-    <row r="29" ht="48" customHeight="1">
+    <row r="29" ht="50.5" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
           <t>When a scan or assessment is past due, the County IT Administrator is notified and the item is completed or rescheduled within 10 business days. Findings from every scan and assessment are recorded in the Vulnerability Assessment Reports and tracked to closure in the Risk / Finding Register.</t>
@@ -1099,10 +1093,8 @@
           <t>/s/ Marcus Reed</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
+      <c r="D41" s="27">
+        <v>46037</v>
       </c>
       <c r="E41" s="15" t="n"/>
       <c r="F41" s="15" t="n"/>
@@ -1123,10 +1115,8 @@
           <t>/s/ Tracy Holloway</t>
         </is>
       </c>
-      <c r="D42" s="15" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
+      <c r="D42" s="27">
+        <v>46037</v>
       </c>
       <c r="E42" s="15" t="n"/>
       <c r="F42" s="15" t="n"/>
@@ -1163,16 +1153,14 @@
       <c r="E45" s="14" t="n"/>
       <c r="F45" s="14" t="n"/>
     </row>
-    <row r="46" ht="17" customHeight="1">
+    <row r="46" ht="34.7" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
+      <c r="B46" s="26">
+        <v>46037</v>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
@@ -1188,11 +1176,11 @@
       <c r="F46" s="12" t="n"/>
     </row>
     <row r="47"/>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" s="2" t="n"/>
+    <row r="48">
+      <c r="A48"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="27">
     <mergeCell ref="A32:G32"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:G6"/>
@@ -1210,7 +1198,6 @@
     <mergeCell ref="A31:G31"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A48:G48"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="A1:G1"/>
@@ -1222,14 +1209,8 @@
     <mergeCell ref="A33:G33"/>
     <mergeCell ref="C3:G3"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="F11:F20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Status" prompt="Select a status" type="list">
-      <formula1>"On track,Due soon,Overdue,Complete"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>